--- a/10_レビュー/レビュー記録_橋爪_2025.12.19.xlsx
+++ b/10_レビュー/レビュー記録_橋爪_2025.12.19.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\sotsuken242310\10_レビュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C086026-8E69-4CCA-ABA1-BC00BFBBB64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85862E4A-39CD-4A5B-B3D1-C84709A9872F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5729C80-F964-450C-B0E5-72837C33B520}"/>
+    <workbookView xWindow="4020" yWindow="3975" windowWidth="13860" windowHeight="12630" xr2:uid="{B5729C80-F964-450C-B0E5-72837C33B520}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー記録" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>参加者</t>
     <rPh sb="0" eb="3">
@@ -224,6 +224,43 @@
     <t>ユーザIDだったところをユーザーネームに変更した</t>
     <rPh sb="20" eb="22">
       <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コメントだけ見るボタン</t>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>dm1ふぉろーのみ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>管理人機能読み込み</t>
+    <rPh sb="0" eb="5">
+      <t>カンリニンキノウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>トレンド、スコア形式、投稿を表示</t>
+    <rPh sb="8" eb="10">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -783,7 +820,9 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="2"/>
       <c r="F13" s="4"/>
@@ -793,8 +832,12 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="E14" s="2"/>
       <c r="F14" s="4"/>
     </row>
@@ -803,7 +846,9 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="2"/>
       <c r="F15" s="4"/>
@@ -813,7 +858,9 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2"/>
       <c r="F16" s="4"/>

--- a/10_レビュー/レビュー記録_橋爪_2025.12.19.xlsx
+++ b/10_レビュー/レビュー記録_橋爪_2025.12.19.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\sotsuken242310\10_レビュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85862E4A-39CD-4A5B-B3D1-C84709A9872F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4121DF8-9F0F-4D43-98A4-C872922089CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="3975" windowWidth="13860" windowHeight="12630" xr2:uid="{B5729C80-F964-450C-B0E5-72837C33B520}"/>
+    <workbookView xWindow="16275" yWindow="6810" windowWidth="9105" windowHeight="12630" xr2:uid="{B5729C80-F964-450C-B0E5-72837C33B520}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー記録" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>参加者</t>
     <rPh sb="0" eb="3">
@@ -823,7 +823,9 @@
       <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="4"/>
     </row>
@@ -849,7 +851,9 @@
       <c r="C15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="F15" s="4"/>
     </row>
@@ -861,7 +865,9 @@
       <c r="C16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="E16" s="2"/>
       <c r="F16" s="4"/>
     </row>
